--- a/tame_output/ON/bt/strategyON_20240204.xlsx
+++ b/tame_output/ON/bt/strategyON_20240204.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.3%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128.5%</t>
+          <t>128.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1862"/>
+  <dimension ref="A1:G1863"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.310840619297879</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44387,6 +44387,29 @@
       </c>
       <c r="G1862" t="n">
         <v>4.473267055940225</v>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" s="2" t="n">
+        <v>45325</v>
+      </c>
+      <c r="B1863" t="n">
+        <v>3.30484768689288</v>
+      </c>
+      <c r="C1863" t="n">
+        <v>3.116678975928913</v>
+      </c>
+      <c r="D1863" t="n">
+        <v>1.646386163391996</v>
+      </c>
+      <c r="E1863" t="n">
+        <v>3.774877016971964</v>
+      </c>
+      <c r="F1863" t="n">
+        <v>2.259404876554754</v>
+      </c>
+      <c r="G1863" t="n">
+        <v>4.472321901861765</v>
       </c>
     </row>
   </sheetData>
